--- a/fFirezone.xlsx
+++ b/fFirezone.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/BI_2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://safbotafogo-my.sharepoint.com/personal/pedro_arruda_safbfr_com_br/Documents/Área de Trabalho/dash-ticket/dash-ticket/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{38FB31E4-F127-427D-B47B-56FEC2F697D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{611D0468-6B24-4DB4-A749-05C0786211D6}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{38FB31E4-F127-427D-B47B-56FEC2F697D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B113F926-15BE-4D1A-8384-BDF9AE33676A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{54CE0D73-6F95-420C-A84C-31E984F0B1C3}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="72">
   <si>
     <t>ID_CAT_FIN_2</t>
   </si>
@@ -213,6 +213,45 @@
   </si>
   <si>
     <t>2025.08.14-CAMLI5-OITAVAS</t>
+  </si>
+  <si>
+    <t>2026.01.21-CAMCA4-3</t>
+  </si>
+  <si>
+    <t>2026.01.24-CAMCA4-4</t>
+  </si>
+  <si>
+    <t>2026.01.29-CAMBR2-1</t>
+  </si>
+  <si>
+    <t>2026.02.01-CAMCA4-5</t>
+  </si>
+  <si>
+    <t>2026.02.15-CAMCA4-Quartas</t>
+  </si>
+  <si>
+    <t>2026.02.25-CAMLI5-2° FASE</t>
+  </si>
+  <si>
+    <t>2026.02.28-CAMCA4-SEMIS - TR</t>
+  </si>
+  <si>
+    <t>2026.03.07-CAMCA4-FINAL - TR</t>
+  </si>
+  <si>
+    <t>2026.03.10-CAMLI5-3° Fase</t>
+  </si>
+  <si>
+    <t>2026.03.14-CAMBR2-6</t>
+  </si>
+  <si>
+    <t>2026.04.01-CAMBR2-9</t>
+  </si>
+  <si>
+    <t>2026.04.09-CAMSU6-FG</t>
+  </si>
+  <si>
+    <t>2026.04.12-CAMBR2-11</t>
   </si>
 </sst>
 </file>
@@ -598,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9379151-0766-40C8-BCCD-C577703F4E7B}">
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.1796875" bestFit="1" customWidth="1"/>
@@ -1307,9 +1346,132 @@
       <c r="B64" t="s">
         <v>58</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="2">
         <v>60900</v>
       </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>2</v>
+      </c>
+      <c r="B65" t="s">
+        <v>59</v>
+      </c>
+      <c r="C65" s="2">
+        <v>5996</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s">
+        <v>60</v>
+      </c>
+      <c r="C66" s="2">
+        <v>15770</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>2</v>
+      </c>
+      <c r="B67" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" s="2">
+        <v>8299</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B68" t="s">
+        <v>62</v>
+      </c>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>2</v>
+      </c>
+      <c r="B69" t="s">
+        <v>63</v>
+      </c>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>2</v>
+      </c>
+      <c r="B70" t="s">
+        <v>64</v>
+      </c>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>2</v>
+      </c>
+      <c r="B71" t="s">
+        <v>65</v>
+      </c>
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>2</v>
+      </c>
+      <c r="B72" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B73" t="s">
+        <v>67</v>
+      </c>
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>2</v>
+      </c>
+      <c r="B74" t="s">
+        <v>68</v>
+      </c>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>2</v>
+      </c>
+      <c r="B75" t="s">
+        <v>69</v>
+      </c>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>2</v>
+      </c>
+      <c r="B76" t="s">
+        <v>70</v>
+      </c>
+      <c r="C76" s="2"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>2</v>
+      </c>
+      <c r="B77" t="s">
+        <v>71</v>
+      </c>
+      <c r="C77" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
